--- a/artfynd/A 13479-2022 artfynd.xlsx
+++ b/artfynd/A 13479-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13479-2022 artfynd.xlsx
+++ b/artfynd/A 13479-2022 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>76936070</v>
       </c>
       <c r="B4" t="n">
-        <v>56249</v>
+        <v>56252</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>76935888</v>
       </c>
       <c r="B6" t="n">
-        <v>56259</v>
+        <v>56262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>119090741</v>
       </c>
       <c r="B8" t="n">
-        <v>56249</v>
+        <v>56252</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 13479-2022 artfynd.xlsx
+++ b/artfynd/A 13479-2022 artfynd.xlsx
@@ -933,7 +933,7 @@
         <v>76936070</v>
       </c>
       <c r="B4" t="n">
-        <v>56252</v>
+        <v>56255</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>76935888</v>
       </c>
       <c r="B6" t="n">
-        <v>56262</v>
+        <v>56265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>119090741</v>
       </c>
       <c r="B8" t="n">
-        <v>56252</v>
+        <v>56255</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 13479-2022 artfynd.xlsx
+++ b/artfynd/A 13479-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119090784</v>
+        <v>119090741</v>
       </c>
       <c r="B7" t="n">
-        <v>56202</v>
+        <v>56255</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,25 +1313,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1376,22 +1376,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-07-31</t>
+          <t>2019-07-30</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>23:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-07-31</t>
+          <t>2019-07-30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Alternativ taigafladdermus</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,142 +1434,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>119090741</v>
-      </c>
-      <c r="B8" t="n">
-        <v>56255</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Myotis daubentonii</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Gergrundet, Vb</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>774106</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7084613</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2019-07-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>23:18</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2019-07-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>23:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Alternativ taigafladdermus</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Landhöjningsskog</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Johan Eklöf</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Marlene Olsson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Marlene Olsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13479-2022 artfynd.xlsx
+++ b/artfynd/A 13479-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76936028</v>
+        <v>76935680</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100086</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dammfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis dasycneme</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(F.Boie, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,21 +712,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gergrundet, Skeppsviks skärgård, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774105.4515752284</v>
+        <v>774105</v>
       </c>
       <c r="R2" t="n">
-        <v>7084612.559556431</v>
+        <v>7084613</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,43 +749,34 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2018-08-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2018-08-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Björn Palmqvist</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Marlene Olsson</t>
@@ -809,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76935871</v>
+        <v>76935808</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,25 +802,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100086</v>
+        <v>100087</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dammfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis dasycneme</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(F.Boie, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -858,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774105.4515752284</v>
+        <v>774105</v>
       </c>
       <c r="R3" t="n">
-        <v>7084612.559556431</v>
+        <v>7084613</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,22 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-08-30</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:33</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-08-30</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:33</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,15 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>76936070</v>
+        <v>76935888</v>
       </c>
       <c r="B4" t="n">
-        <v>56255</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,25 +922,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -1009,22 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>03:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>03:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,32 +1031,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76935808</v>
+        <v>76936070</v>
       </c>
       <c r="B5" t="n">
-        <v>57495</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100087</v>
+        <v>205992</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,11 +1060,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1104,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774105.4515752284</v>
+        <v>774105</v>
       </c>
       <c r="R5" t="n">
-        <v>7084612.559556431</v>
+        <v>7084613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,29 +1105,29 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1176,15 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76935888</v>
+        <v>119082251</v>
       </c>
       <c r="B6" t="n">
-        <v>56265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,29 +1158,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1225,11 +1187,11 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gergrundet, Skeppsviks skärgård, Vb</t>
+          <t>Gergrundet, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774105</v>
+        <v>774106</v>
       </c>
       <c r="R6" t="n">
         <v>7084613</v>
@@ -1259,22 +1221,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-09-04</t>
+          <t>2019-07-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>03:03</t>
+          <t>02:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-09-04</t>
+          <t>2019-07-27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>03:03</t>
+          <t>02:31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Alternativ taigafladdermus</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,7 +1253,21 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Landhöjningsblandskog</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Johan Eklöf</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>Marlene Olsson</t>
@@ -1301,40 +1282,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119090741</v>
+        <v>76936028</v>
       </c>
       <c r="B7" t="n">
-        <v>56255</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -1342,11 +1326,11 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gergrundet, Vb</t>
+          <t>Gergrundet, Skeppsviks skärgård, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774106</v>
+        <v>774105</v>
       </c>
       <c r="R7" t="n">
         <v>7084613</v>
@@ -1376,64 +1360,188 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>2018-08-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-08-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Björn Palmqvist</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marlene Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marlene Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119082247</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gergrundet, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>774106</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7084613</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>2019-07-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>23:18</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2019-07-30</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>23:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Alternativ taigafladdermus</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Landhöjningsskog</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Landhöjningsblandskog</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
         <is>
           <t>Johan Eklöf</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>Marlene Olsson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Marlene Olsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13479-2022 artfynd.xlsx
+++ b/artfynd/A 13479-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76935680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76935808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76935888</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76936070</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1304,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119082251</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1408,6 +1438,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76936028</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1542,8 +1577,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119082247</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>